--- a/docs/platform/p1-kit/boards/board-01-business.xlsx
+++ b/docs/platform/p1-kit/boards/board-01-business.xlsx
@@ -9,8 +9,9 @@
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="記録" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="ボード" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="前提" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="記録" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="ボード" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <r>
       <rPr>
@@ -57,7 +58,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -66,7 +66,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -76,114 +75,118 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回、「記録」シートの黄色の欄に先月の事務作業時間と</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回、「記録」シートの「実績」に、先月の事務作業の合計時間（時間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">化した業務の数を入れてください。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「ボード」シートで、目標と現在地がグラフで分かります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月次更新プランでは、この数字をもとに運営者が計画を更新します。</t>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）を入れてください。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">入れると「ボード」シートで、現在地・目標までの進み具合・必要なペース・期限内に届く見込みが自動で計算され、残りの月の予定も作り直されます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「前提」シートの値は初回の計画書から転記します（月次更新プランでは運営者が見直します）。</t>
   </si>
   <si>
     <t xml:space="preserve">凡例</t>
   </si>
   <si>
-    <t xml:space="preserve">黄色のセル＝あなたが入力する欄（青字）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白いセル＝自動計算（触らない）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+    <t xml:space="preserve">黄色のセル（青字）＝あなたが入力する欄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">緑のセル＝自動で計算される「現在地」と「これからの予定」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その他の白いセル＝自動計算（触らない）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入っている数字は架空の記入例です。上書きしてお使いください。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">このシートは、入力した数字から機械的に計算した目安です。結果を保証するものではありません。氏名・口座番号・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">行目の数字は記入例（架空）です。上書きしてお使いください。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">このシートは目安を可視化するもので、結果を保証するものではありません。氏名・口座番号・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve">ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・パスワード・学校名などは書かないでください。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">前提（初回の計画書から転記）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">事務作業時間：最初の値（時間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">ID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・パスワードなどは書かないでください。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">月</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">目標の事務作業時間（時間</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">事務作業時間：目標の値（時間</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
@@ -193,23 +196,28 @@
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">期限までの月数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <b val="true"/>
         <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">実績の事務作業時間（時間</t>
+      <t xml:space="preserve">当初の計画（時間</t>
     </r>
     <r>
       <rPr>
@@ -232,9 +240,15 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">差（実績−目標）</t>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実績（時間</t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -243,7 +257,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">AI</t>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
@@ -252,158 +266,71 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">化した業務の数（累計）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">メモ（個人情報は書かない）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
+      <t xml:space="preserve">月）※入力</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">更新後の予定（時間</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今のペースが続いた場合（時間</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">※ 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目以降の数値も架空の記入例です。目標は初回の計画書から転記します。</t>
-    </r>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 入力するのは「実績」の列だけです。月ごとに上から順に入れてください。</t>
   </si>
   <si>
     <r>
@@ -436,19 +363,23 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">最初の事務作業時間（時間</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+    <t xml:space="preserve">現在地</t>
+  </si>
+  <si>
+    <t xml:space="preserve">記録した月数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現在の事務作業時間（時間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -458,7 +389,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -469,16 +399,14 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">最新の実績（時間</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標（時間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -488,7 +416,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -496,49 +423,43 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">最終目標（時間</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+    <t xml:space="preserve">目標までの進み具合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当初の計画と比べて</t>
+  </si>
+  <si>
+    <t xml:space="preserve">残りの月数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標に届くために必要な</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">削減できた時間（時間</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月あたりの変化（時間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -548,7 +469,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -556,27 +476,134 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">目標までの達成率</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">これまでの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月あたりの平均の変化（時間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">今のペースで目標に届く見込み</t>
+  </si>
+  <si>
+    <t xml:space="preserve">これからの予定（自動更新）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「記録」シートの「更新後の予定」列に、残りの月ごとに目指す値が自動で入ります。実績を入れるたびに作り直されます。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">AI</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">化した業務の数</t>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">化した業務</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">化する予定の業務の数</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">化が終わった業務の数（入力）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">化の進み具合</t>
     </r>
   </si>
 </sst>
@@ -584,14 +611,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.0;\-0.0;0"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="0%"/>
-    <numFmt numFmtId="168" formatCode="0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -629,13 +655,11 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -653,13 +677,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
@@ -667,6 +684,7 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -700,7 +718,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -710,13 +728,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFDDE6F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDE6F5"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -769,7 +793,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -790,44 +814,52 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -875,7 +907,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFE2F0D9"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -883,7 +915,7 @@
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF98B855"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
@@ -928,7 +960,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>事務作業時間：目標と実績</a:t>
+              <a:t>当初の計画・実績・更新後の予定</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -955,7 +987,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>目標の事務作業時間（時間/月）</c:v>
+                  <c:v>当初の計画（時間/月）</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1005,22 +1037,22 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1か月目</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2か月目</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3か月目</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4か月目</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5か月目</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6か月目</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1029,22 +1061,22 @@
             <c:numRef>
               <c:f>記録!$B$2:$B$7</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>22</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>10</c:v>
@@ -1063,7 +1095,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>実績の事務作業時間（時間/月）</c:v>
+                  <c:v>実績（時間/月）※入力</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1113,22 +1145,22 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1か月目</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2か月目</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3か月目</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4か月目</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5か月目</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6か月目</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1137,7 +1169,7 @@
             <c:numRef>
               <c:f>記録!$C$2:$C$7</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>22</c:v>
@@ -1147,6 +1179,105 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>記録!D1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>更新後の予定（時間/月）</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>記録!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>記録!$D$2:$D$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1161,17 +1292,17 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="48685184"/>
-        <c:axId val="14554288"/>
+        <c:axId val="2624612"/>
+        <c:axId val="94675111"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="48685184"/>
+        <c:axId val="2624612"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1197,7 +1328,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14554288"/>
+        <c:crossAx val="94675111"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1205,7 +1336,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="14554288"/>
+        <c:axId val="94675111"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1255,7 +1386,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1281,7 +1412,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48685184"/>
+        <c:crossAx val="2624612"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1337,16 +1468,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>106560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>364680</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>473040</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>182520</xdr:rowOff>
+      <xdr:rowOff>36000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1354,8 +1485,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3853800" y="380880"/>
-        <a:ext cx="6479640" cy="2879640"/>
+        <a:off x="7896240" y="380880"/>
+        <a:ext cx="7199640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1548,10 +1679,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1585,18 +1716,23 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1615,141 +1751,40 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="B2" s="7" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="B3" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="C2" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="D2" s="9" t="n">
-        <f aca="false">IF(C2="","",C2-B2)</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="C3" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" s="9" t="n">
-        <f aca="false">IF(C3="","",C3-B3)</f>
-        <v>1</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="8"/>
-    </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="B4" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="C4" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <f aca="false">IF(C4="","",C4-B4)</f>
-        <v>1</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="8"/>
-    </row>
-    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="9" t="str">
-        <f aca="false">IF(C5="","",C5-B5)</f>
-        <v/>
-      </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-    </row>
-    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9" t="str">
-        <f aca="false">IF(C6="","",C6-B6)</f>
-        <v/>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="9" t="str">
-        <f aca="false">IF(C7="","",C7-B7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1768,70 +1803,302 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A2/前提!$B$4</f>
+        <v>20</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2" s="11" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4))</f>
+        <v/>
+      </c>
+      <c r="E2" s="11" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A2-ボード!$B$4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A3/前提!$B$4</f>
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" s="11" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4))</f>
+        <v/>
+      </c>
+      <c r="E3" s="11" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A3-ボード!$B$4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A4/前提!$B$4</f>
+        <v>16</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" s="11" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4))</f>
+        <v/>
+      </c>
+      <c r="E4" s="11" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A4-ボード!$B$4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A5/前提!$B$4</f>
+        <v>14</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4))</f>
+        <v>14</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A5-ボード!$B$4))</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A6/前提!$B$4</f>
+        <v>12</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4))</f>
+        <v>12</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A6-ボード!$B$4))</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A7/前提!$B$4</f>
+        <v>10</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4))</f>
+        <v>10</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A7-ボード!$B$4))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="B4" s="10" t="n">
+        <f aca="false">IF(COUNT(記録!C2:C7)=0,"",COUNT(記録!C2:C7))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="11" t="n">
-        <f aca="false">記録!C2</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="B5" s="12" t="n">
+        <f aca="false">IF(B4="","",LOOKUP(2,1/(記録!C2:C7&lt;&gt;""),記録!C2:C7))</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="11" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(記録!C2:C7&lt;&gt;""),記録!C2:C7),"")</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
+      <c r="B6" s="11" t="n">
+        <f aca="false">前提!B3</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="11" t="n">
-        <f aca="false">記録!B7</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
+      <c r="B7" s="13" t="n">
+        <f aca="false">IFERROR((B5-前提!B2)/(前提!B3-前提!B2),"")</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="11" t="n">
-        <f aca="false">IFERROR(B3-B4,"")</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+      <c r="B8" s="14" t="str">
+        <f aca="false">IF(B4="","",IF((B5-INDEX(記録!B2:B7,B4))*SIGN(前提!B3-前提!B2)&gt;=0,"計画どおり、または先行","計画より遅れ"))</f>
+        <v>計画どおり、または先行</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="12" t="n">
-        <f aca="false">IFERROR((B3-B4)/(B3-B5),"")</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+      <c r="B9" s="10" t="n">
+        <f aca="false">IF(B4="","",前提!B4-B4)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="14" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(記録!E2:E7&lt;&gt;""),記録!E2:E7),"")</f>
+      <c r="B10" s="12" t="n">
+        <f aca="false">IFERROR(IF(B9&lt;=0,"",(前提!B3-B5)/B9),"")</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="11" t="n">
+        <f aca="false">IFERROR((B5-前提!B2)/B4,"")</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="14" t="str">
+        <f aca="false">IFERROR(IF((前提!B3-B5)*SIGN(前提!B3-前提!B2)&lt;=0,"達成済み",IF(B11*SIGN(前提!B3-前提!B2)&lt;=0,"今のペースでは届かない（計画の見直しが必要）",IF(B4+(前提!B3-B5)/B11&lt;=前提!B4,"期限内（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）","期限より遅れる（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）"))),"")</f>
+        <v>期限内（6か月目ごろ）</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="8" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="13" t="n">
+        <f aca="false">IFERROR(B19/B18,"")</f>
+        <v>0.666666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/docs/platform/p1-kit/boards/board-01-business.xlsx
+++ b/docs/platform/p1-kit/boards/board-01-business.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <r>
       <rPr>
@@ -366,7 +366,7 @@
     <t xml:space="preserve">現在地</t>
   </si>
   <si>
-    <t xml:space="preserve">記録した月数</t>
+    <t xml:space="preserve">最後に実績を入れた月</t>
   </si>
   <si>
     <r>
@@ -520,7 +520,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">今のペースで目標に届く見込み</t>
+    <t xml:space="preserve">今のペースで目標に届く見込み（過去の数値を直線で延ばした参考計算）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入力のチェック</t>
   </si>
   <si>
     <t xml:space="preserve">これからの予定（自動更新）</t>
@@ -793,7 +796,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -851,6 +854,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1292,11 +1299,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="2624612"/>
-        <c:axId val="94675111"/>
+        <c:axId val="7016875"/>
+        <c:axId val="53125286"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="2624612"/>
+        <c:axId val="7016875"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1328,7 +1335,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94675111"/>
+        <c:crossAx val="53125286"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1336,7 +1343,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94675111"/>
+        <c:axId val="53125286"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1412,7 +1419,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2624612"/>
+        <c:crossAx val="7016875"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1476,8 +1483,8 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>36000</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>360</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1788,6 +1795,12 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B4" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1840,11 +1853,11 @@
         <v>22</v>
       </c>
       <c r="D2" s="11" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A2&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4)),"")</f>
         <v/>
       </c>
       <c r="E2" s="11" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A2-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A2-ボード!$B$4)),"")</f>
         <v/>
       </c>
     </row>
@@ -1860,11 +1873,11 @@
         <v>20</v>
       </c>
       <c r="D3" s="11" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A3&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4)),"")</f>
         <v/>
       </c>
       <c r="E3" s="11" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A3-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A3-ボード!$B$4)),"")</f>
         <v/>
       </c>
     </row>
@@ -1880,11 +1893,11 @@
         <v>16</v>
       </c>
       <c r="D4" s="11" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A4&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4)),"")</f>
         <v/>
       </c>
       <c r="E4" s="11" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A4-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A4-ボード!$B$4)),"")</f>
         <v/>
       </c>
     </row>
@@ -1898,11 +1911,11 @@
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A5&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4)),"")</f>
         <v>14</v>
       </c>
       <c r="E5" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A5-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A5-ボード!$B$4)),"")</f>
         <v>14</v>
       </c>
     </row>
@@ -1916,11 +1929,11 @@
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A6&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4)),"")</f>
         <v>12</v>
       </c>
       <c r="E6" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A6-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A6-ボード!$B$4)),"")</f>
         <v>12</v>
       </c>
     </row>
@@ -1934,11 +1947,11 @@
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A7&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4)),"")</f>
         <v>10</v>
       </c>
       <c r="E7" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A7-ボード!$B$4))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A7-ボード!$B$4)),"")</f>
         <v>10</v>
       </c>
     </row>
@@ -1948,6 +1961,12 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C7" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1963,7 +1982,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -1985,7 +2004,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="10" t="n">
-        <f aca="false">IF(COUNT(記録!C2:C7)=0,"",COUNT(記録!C2:C7))</f>
+        <f aca="false">IF(COUNT(記録!C2:C7)=0,"",LOOKUP(2,1/(記録!C2:C7&lt;&gt;""),記録!A2:A7))</f>
         <v>3</v>
       </c>
     </row>
@@ -2012,7 +2031,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="13" t="n">
-        <f aca="false">IFERROR((B5-前提!B2)/(前提!B3-前提!B2),"")</f>
+        <f aca="false">IF(OR(B4="",(前提!B3-前提!B2)=0),"",(B5-前提!B2)/(前提!B3-前提!B2))</f>
         <v>0.5</v>
       </c>
     </row>
@@ -2021,7 +2040,7 @@
         <v>26</v>
       </c>
       <c r="B8" s="14" t="str">
-        <f aca="false">IF(B4="","",IF((B5-INDEX(記録!B2:B7,B4))*SIGN(前提!B3-前提!B2)&gt;=0,"計画どおり、または先行","計画より遅れ"))</f>
+        <f aca="false">IF(B4="","",IF((前提!B3-前提!B2)=0,"前提を確認（最初の値と目標が同じ）",IF((B5-INDEX(記録!B2:B7,B4))*SIGN((前提!B3-前提!B2))&gt;=0,"計画どおり、または先行","計画より遅れ")))</f>
         <v>計画どおり、または先行</v>
       </c>
     </row>
@@ -2039,7 +2058,7 @@
         <v>28</v>
       </c>
       <c r="B10" s="12" t="n">
-        <f aca="false">IFERROR(IF(B9&lt;=0,"",(前提!B3-B5)/B9),"")</f>
+        <f aca="false">IF(OR(B4="",(前提!B3-前提!B2)=0),"",IF((前提!B3-B5)*SIGN((前提!B3-前提!B2))&lt;=0,0,IF(B9&lt;=0,"",(前提!B3-B5)/B9)))</f>
         <v>-2</v>
       </c>
     </row>
@@ -2048,31 +2067,35 @@
         <v>29</v>
       </c>
       <c r="B11" s="11" t="n">
-        <f aca="false">IFERROR((B5-前提!B2)/B4,"")</f>
+        <f aca="false">IF(COUNT(記録!C2:C7)&lt;2,"",(B5-前提!B2)/B4)</f>
         <v>-2</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B12" s="14" t="str">
-        <f aca="false">IFERROR(IF((前提!B3-B5)*SIGN(前提!B3-前提!B2)&lt;=0,"達成済み",IF(B11*SIGN(前提!B3-前提!B2)&lt;=0,"今のペースでは届かない（計画の見直しが必要）",IF(B4+(前提!B3-B5)/B11&lt;=前提!B4,"期限内（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）","期限より遅れる（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）"))),"")</f>
+        <f aca="false">IF(B4="","",IF((前提!B3-前提!B2)=0,"前提を確認（最初の値と目標が同じ）",IF((前提!B3-B5)*SIGN((前提!B3-前提!B2))&lt;=0,"達成済み",IF(B9&lt;=0,"期限を過ぎています（前提の見直しが必要）",IF(COUNT(記録!C2:C7)&lt;2,"記録が2か月分以上で表示",IF(B11*SIGN((前提!B3-前提!B2))&lt;=0,"今のペースでは届かない（計画の見直しが必要）",IF(B4+(前提!B3-B5)/B11&lt;=前提!B4,"期限内（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）","期限より遅れる（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）")))))))</f>
         <v>期限内（6か月目ごろ）</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>31</v>
       </c>
+      <c r="B13" s="15" t="str">
+        <f aca="false">IF(COUNTIF(記録!C2:C7,"&lt;0")&gt;0,"マイナスの値があります。確認してください",IF(B4="","実績を入力してください",IF(COUNT(記録!C2:C7)&lt;B4,"入力していない月があります（現在地は最後に入力した月で計算）","OK")))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2080,28 +2103,39 @@
       <c r="A18" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="8" t="n">
+    </row>
+    <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="8" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="8" t="n">
+    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="13" t="n">
-        <f aca="false">IFERROR(B19/B18,"")</f>
+    <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="13" t="n">
+        <f aca="false">IF(OR(B19="",B19&lt;=0),"",MIN(B20/B19,1))</f>
         <v>0.666666666666667</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B19:B20" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/docs/platform/p1-kit/boards/board-01-business.xlsx
+++ b/docs/platform/p1-kit/boards/board-01-business.xlsx
@@ -8,10 +8,11 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="使い方" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="前提" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="記録" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="ボード" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="スマホ" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="使い方" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="前提" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="記録" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="ボード" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,294 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">① スマホで見る：</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">業務改善</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 現在地</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在地</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目標</t>
+  </si>
+  <si>
+    <t xml:space="preserve">進み具合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">計画と比べて</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">必要なペース（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月あたり）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">見込み（参考計算）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入力のチェック</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">単位：時間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月。見込みは過去の数値を直線で延ばした参考計算です。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">■ 毎月の数字を入れる：事務作業時間（時間</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">化が終わった業務の数</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">化の進み具合</t>
+    </r>
+  </si>
   <si>
     <r>
       <rPr>
@@ -78,7 +366,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">回、「記録」シートの「実績」に、先月の事務作業の合計時間（時間</t>
+      <t xml:space="preserve">回、「スマホ」シートの下にある「毎月の数字を入れる」欄に、先月の事務作業の合計時間（時間</t>
     </r>
     <r>
       <rPr>
@@ -266,7 +554,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月）※入力</t>
+      <t xml:space="preserve">月）※スマホのシートから自動</t>
     </r>
   </si>
   <si>
@@ -330,7 +618,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">※ 入力するのは「実績」の列だけです。月ごとに上から順に入れてください。</t>
+    <t xml:space="preserve">※ 実績は「スマホ」シートで入力します（この列は自動）。</t>
   </si>
   <si>
     <r>
@@ -363,9 +651,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">現在地</t>
-  </si>
-  <si>
     <t xml:space="preserve">最後に実績を入れた月</t>
   </si>
   <si>
@@ -523,9 +808,6 @@
     <t xml:space="preserve">今のペースで目標に届く見込み（過去の数値を直線で延ばした参考計算）</t>
   </si>
   <si>
-    <t xml:space="preserve">入力のチェック</t>
-  </si>
-  <si>
     <t xml:space="preserve">これからの予定（自動更新）</t>
   </si>
   <si>
@@ -587,26 +869,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">化が終わった業務の数（入力）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">化の進み具合</t>
+      <t xml:space="preserve">化が終わった業務の数（スマホのシートから自動）</t>
     </r>
   </si>
 </sst>
@@ -617,10 +880,10 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0"/>
-    <numFmt numFmtId="167" formatCode="0%"/>
+    <numFmt numFmtId="166" formatCode="0%"/>
+    <numFmt numFmtId="167" formatCode="0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -645,24 +908,13 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="14"/>
+      <sz val="13"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="14"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="13"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -675,20 +927,36 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -720,6 +988,25 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -730,14 +1017,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFE2F0D9"/>
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFDDE6F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2F0D9"/>
-        <bgColor rgb="FFDDE6F5"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -796,77 +1083,101 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -967,7 +1278,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>当初の計画・実績・更新後の予定</a:t>
+              <a:t>計画・実績・予定</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -990,11 +1301,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>記録!B1</c:f>
+              <c:f>"当初の計画"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>当初の計画（時間/月）</c:v>
+                  <c:v>当初の計画</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1098,11 +1409,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>記録!C1</c:f>
+              <c:f>"実績"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>実績（時間/月）※入力</c:v>
+                  <c:v>実績</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1174,7 +1485,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>記録!$C$2:$C$7</c:f>
+              <c:f>スマホ!$B$27:$B$32</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1197,11 +1508,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>記録!D1</c:f>
+              <c:f>"更新後の予定"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>更新後の予定（時間/月）</c:v>
+                  <c:v>更新後の予定</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1299,11 +1610,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="7016875"/>
-        <c:axId val="53125286"/>
+        <c:axId val="82358082"/>
+        <c:axId val="67869853"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="7016875"/>
+        <c:axId val="82358082"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1335,7 +1646,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53125286"/>
+        <c:crossAx val="67869853"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1343,7 +1654,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53125286"/>
+        <c:axId val="67869853"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1419,7 +1730,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7016875"/>
+        <c:crossAx val="82358082"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1431,7 +1742,537 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>当初の計画・実績・更新後の予定</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"当初の計画"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>当初の計画</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>記録!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>記録!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"実績"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>実績</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>記録!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>スマホ!$B$27:$B$32</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"更新後の予定"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>更新後の予定</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>記録!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>記録!$D$2:$D$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="62349445"/>
+        <c:axId val="73363721"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="62349445"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="73363721"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="73363721"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>時間/月</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="62349445"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1475,6 +2316,41 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>593280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>129600</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>122040</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="5143680"/>
+        <a:ext cx="3419640" cy="2519640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
@@ -1488,7 +2364,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvPr id="1" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1686,63 +2562,166 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="38.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="3" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="B3" s="4" t="n">
+        <f aca="false">ボード!B5</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="n">
+        <f aca="false">ボード!B6</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <f aca="false">ボード!B7</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="str">
+        <f aca="false">ボード!B8</f>
+        <v>計画どおり、または先行</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="B7" s="5" t="n">
+        <f aca="false">ボード!B10</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="B8" s="7" t="str">
+        <f aca="false">ボード!B12</f>
+        <v>期限内（6か月目ごろ）</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="B9" s="3" t="str">
+        <f aca="false">ボード!B13</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
         <v>9</v>
       </c>
+      <c r="B10" s="8"/>
+    </row>
+    <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="10"/>
+    </row>
+    <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="10"/>
+    </row>
+    <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="10"/>
+    </row>
+    <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="6" t="n">
+        <f aca="false">ボード!B21</f>
+        <v>0.666666666666667</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:B10"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B27:B32 B34" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1750,6 +2729,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1758,49 +2738,63 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="7" t="n">
+    <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="7" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="8" t="n">
-        <v>6</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B4" type="decimal">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1816,153 +2810,45 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="n">
-        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A2/前提!$B$4</f>
-        <v>20</v>
-      </c>
-      <c r="C2" s="7" t="n">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="D2" s="11" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A2&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4)),"")</f>
-        <v/>
-      </c>
-      <c r="E2" s="11" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A2-ボード!$B$4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="n">
-        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A3/前提!$B$4</f>
-        <v>18</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" s="11" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A3&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4)),"")</f>
-        <v/>
-      </c>
-      <c r="E3" s="11" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A3-ボード!$B$4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="n">
-        <v>3</v>
+    </row>
+    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="B4" s="11" t="n">
-        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A4/前提!$B$4</f>
-        <v>16</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="D4" s="11" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A4&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4)),"")</f>
-        <v/>
-      </c>
-      <c r="E4" s="11" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A4-ボード!$B$4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="n">
-        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A5/前提!$B$4</f>
-        <v>14</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A5&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4)),"")</f>
-        <v>14</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A5-ボード!$B$4)),"")</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="11" t="n">
-        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A6/前提!$B$4</f>
-        <v>12</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A6&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4)),"")</f>
-        <v>12</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A6-ボード!$B$4)),"")</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="n">
         <v>6</v>
-      </c>
-      <c r="B7" s="11" t="n">
-        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A7/前提!$B$4</f>
-        <v>10</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A7&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4)),"")</f>
-        <v>10</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A7-ボード!$B$4)),"")</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C7" type="decimal">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B4" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1982,6 +2868,178 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A2/前提!$B$4</f>
+        <v>20</v>
+      </c>
+      <c r="C2" s="18" t="n">
+        <f aca="false">IF(スマホ!B27="","",スマホ!B27)</f>
+        <v>22</v>
+      </c>
+      <c r="D2" s="18" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A2&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4)),"")</f>
+        <v/>
+      </c>
+      <c r="E2" s="18" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A2-ボード!$B$4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A3/前提!$B$4</f>
+        <v>18</v>
+      </c>
+      <c r="C3" s="18" t="n">
+        <f aca="false">IF(スマホ!B28="","",スマホ!B28)</f>
+        <v>20</v>
+      </c>
+      <c r="D3" s="18" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A3&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4)),"")</f>
+        <v/>
+      </c>
+      <c r="E3" s="18" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A3-ボード!$B$4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A4/前提!$B$4</f>
+        <v>16</v>
+      </c>
+      <c r="C4" s="18" t="n">
+        <f aca="false">IF(スマホ!B29="","",スマホ!B29)</f>
+        <v>16</v>
+      </c>
+      <c r="D4" s="18" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A4&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4)),"")</f>
+        <v/>
+      </c>
+      <c r="E4" s="18" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A4-ボード!$B$4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="18" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A5/前提!$B$4</f>
+        <v>14</v>
+      </c>
+      <c r="C5" s="18" t="str">
+        <f aca="false">IF(スマホ!B30="","",スマホ!B30)</f>
+        <v/>
+      </c>
+      <c r="D5" s="18" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A5&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4)),"")</f>
+        <v>14</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A5-ボード!$B$4)),"")</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A6/前提!$B$4</f>
+        <v>12</v>
+      </c>
+      <c r="C6" s="18" t="str">
+        <f aca="false">IF(スマホ!B31="","",スマホ!B31)</f>
+        <v/>
+      </c>
+      <c r="D6" s="18" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A6&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4)),"")</f>
+        <v>12</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A6-ボード!$B$4)),"")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="18" t="n">
+        <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A7/前提!$B$4</f>
+        <v>10</v>
+      </c>
+      <c r="C7" s="18" t="str">
+        <f aca="false">IF(スマホ!B32="","",スマホ!B32)</f>
+        <v/>
+      </c>
+      <c r="D7" s="18" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A7&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4)),"")</f>
+        <v>10</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A7-ボード!$B$4)),"")</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1990,148 +3048,149 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
+      <c r="A1" s="12" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>21</v>
+      <c r="A3" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="10" t="n">
+      <c r="A4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="17" t="n">
         <f aca="false">IF(COUNT(記録!C2:C7)=0,"",LOOKUP(2,1/(記録!C2:C7&lt;&gt;""),記録!A2:A7))</f>
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="12" t="n">
+      <c r="A5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="19" t="n">
         <f aca="false">IF(B4="","",LOOKUP(2,1/(記録!C2:C7&lt;&gt;""),記録!C2:C7))</f>
         <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="11" t="n">
+      <c r="A6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="18" t="n">
         <f aca="false">前提!B3</f>
         <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="13" t="n">
+      <c r="A7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="20" t="n">
         <f aca="false">IF(OR(B4="",(前提!B3-前提!B2)=0),"",(B5-前提!B2)/(前提!B3-前提!B2))</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="14" t="str">
+      <c r="A8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="21" t="str">
         <f aca="false">IF(B4="","",IF((前提!B3-前提!B2)=0,"前提を確認（最初の値と目標が同じ）",IF((B5-INDEX(記録!B2:B7,B4))*SIGN((前提!B3-前提!B2))&gt;=0,"計画どおり、または先行","計画より遅れ")))</f>
         <v>計画どおり、または先行</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="10" t="n">
+      <c r="A9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="17" t="n">
         <f aca="false">IF(B4="","",前提!B4-B4)</f>
         <v>3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="12" t="n">
+      <c r="A10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="19" t="n">
         <f aca="false">IF(OR(B4="",(前提!B3-前提!B2)=0),"",IF((前提!B3-B5)*SIGN((前提!B3-前提!B2))&lt;=0,0,IF(B9&lt;=0,"",(前提!B3-B5)/B9)))</f>
         <v>-2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="11" t="n">
+      <c r="A11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="18" t="n">
         <f aca="false">IF(COUNT(記録!C2:C7)&lt;2,"",(B5-前提!B2)/B4)</f>
         <v>-2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="14" t="str">
+      <c r="A12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="21" t="str">
         <f aca="false">IF(B4="","",IF((前提!B3-前提!B2)=0,"前提を確認（最初の値と目標が同じ）",IF((前提!B3-B5)*SIGN((前提!B3-前提!B2))&lt;=0,"達成済み",IF(B9&lt;=0,"期限を過ぎています（前提の見直しが必要）",IF(COUNT(記録!C2:C7)&lt;2,"記録が2か月分以上で表示",IF(B11*SIGN((前提!B3-前提!B2))&lt;=0,"今のペースでは届かない（計画の見直しが必要）",IF(B4+(前提!B3-B5)/B11&lt;=前提!B4,"期限内（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）","期限より遅れる（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）")))))))</f>
         <v>期限内（6か月目ごろ）</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="15" t="str">
+      <c r="A13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="22" t="str">
         <f aca="false">IF(COUNTIF(記録!C2:C7,"&lt;0")&gt;0,"マイナスの値があります。確認してください",IF(B4="","実績を入力してください",IF(COUNT(記録!C2:C7)&lt;B4,"入力していない月があります（現在地は最後に入力した月で計算）","OK")))</f>
         <v>OK</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>32</v>
+      <c r="A15" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>33</v>
+      <c r="A16" s="13" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
-        <v>34</v>
+      <c r="A18" s="23" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="8" t="n">
+      <c r="A19" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="11" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="8" t="n">
+    <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="17" t="n">
+        <f aca="false">スマホ!B34</f>
         <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="13" t="n">
+      <c r="A21" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="20" t="n">
         <f aca="false">IF(OR(B19="",B19&lt;=0),"",MIN(B20/B19,1))</f>
         <v>0.666666666666667</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B19:B20" type="decimal">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B19" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/docs/platform/p1-kit/boards/board-01-business.xlsx
+++ b/docs/platform/p1-kit/boards/board-01-business.xlsx
@@ -1610,11 +1610,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="82358082"/>
-        <c:axId val="67869853"/>
+        <c:axId val="75999190"/>
+        <c:axId val="61002063"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="82358082"/>
+        <c:axId val="75999190"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1646,7 +1646,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67869853"/>
+        <c:crossAx val="61002063"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1654,7 +1654,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67869853"/>
+        <c:axId val="61002063"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1730,7 +1730,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82358082"/>
+        <c:crossAx val="75999190"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2140,11 +2140,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="62349445"/>
-        <c:axId val="73363721"/>
+        <c:axId val="87646324"/>
+        <c:axId val="13568112"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="62349445"/>
+        <c:axId val="87646324"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2176,7 +2176,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73363721"/>
+        <c:crossAx val="13568112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2184,7 +2184,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73363721"/>
+        <c:axId val="13568112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2260,7 +2260,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62349445"/>
+        <c:crossAx val="87646324"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3062,7 +3062,7 @@
         <v>40</v>
       </c>
       <c r="B4" s="17" t="n">
-        <f aca="false">IF(COUNT(記録!C2:C7)=0,"",LOOKUP(2,1/(記録!C2:C7&lt;&gt;""),記録!A2:A7))</f>
+        <f aca="false">IF(COUNT(記録!C2:C7)=0,"",INDEX(記録!A2:A7,MATCH(9.99E+307,記録!C2:C7)))</f>
         <v>3</v>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
         <v>41</v>
       </c>
       <c r="B5" s="19" t="n">
-        <f aca="false">IF(B4="","",LOOKUP(2,1/(記録!C2:C7&lt;&gt;""),記録!C2:C7))</f>
+        <f aca="false">IF(B4="","",INDEX(記録!C2:C7,MATCH(9.99E+307,記録!C2:C7)))</f>
         <v>16</v>
       </c>
     </row>

--- a/docs/platform/p1-kit/boards/board-01-business.xlsx
+++ b/docs/platform/p1-kit/boards/board-01-business.xlsx
@@ -1083,7 +1083,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1118,6 +1118,10 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1610,11 +1614,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="75999190"/>
-        <c:axId val="61002063"/>
+        <c:axId val="56242545"/>
+        <c:axId val="22367625"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="75999190"/>
+        <c:axId val="56242545"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1646,7 +1650,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61002063"/>
+        <c:crossAx val="22367625"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1654,7 +1658,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="61002063"/>
+        <c:axId val="22367625"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1730,7 +1734,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75999190"/>
+        <c:crossAx val="56242545"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2140,11 +2144,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="87646324"/>
-        <c:axId val="13568112"/>
+        <c:axId val="30219136"/>
+        <c:axId val="66487922"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="87646324"/>
+        <c:axId val="30219136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2176,7 +2180,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13568112"/>
+        <c:crossAx val="66487922"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2184,7 +2188,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13568112"/>
+        <c:axId val="66487922"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2260,7 +2264,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87646324"/>
+        <c:crossAx val="30219136"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2649,62 +2653,63 @@
       <c r="B10" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="9" t="s">
         <v>10</v>
       </c>
+      <c r="B26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="10" t="n">
+      <c r="B27" s="11" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="10" t="n">
+      <c r="B28" s="11" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="10" t="n">
+      <c r="B29" s="11" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="10"/>
+      <c r="B30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="10"/>
+      <c r="B31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="10"/>
+      <c r="B32" s="11"/>
     </row>
     <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="11" t="n">
+      <c r="B34" s="12" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B35" s="6" t="n">
@@ -2713,8 +2718,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A26:B26"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B27:B32 B34" type="decimal">
@@ -2745,22 +2751,22 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2770,27 +2776,27 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="14" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="14" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2826,7 +2832,7 @@
       <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="11" t="n">
         <v>22</v>
       </c>
     </row>
@@ -2834,7 +2840,7 @@
       <c r="A3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2842,7 +2848,7 @@
       <c r="A4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="12" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2877,150 +2883,150 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="17" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="n">
+      <c r="A2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="n">
+      <c r="B2" s="19" t="n">
         <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A2/前提!$B$4</f>
         <v>20</v>
       </c>
-      <c r="C2" s="18" t="n">
+      <c r="C2" s="19" t="n">
         <f aca="false">IF(スマホ!B27="","",スマホ!B27)</f>
         <v>22</v>
       </c>
-      <c r="D2" s="18" t="str">
+      <c r="D2" s="19" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A2&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4)),"")</f>
         <v/>
       </c>
-      <c r="E2" s="18" t="str">
+      <c r="E2" s="19" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A2-ボード!$B$4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="n">
+      <c r="A3" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="18" t="n">
+      <c r="B3" s="19" t="n">
         <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A3/前提!$B$4</f>
         <v>18</v>
       </c>
-      <c r="C3" s="18" t="n">
+      <c r="C3" s="19" t="n">
         <f aca="false">IF(スマホ!B28="","",スマホ!B28)</f>
         <v>20</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="19" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A3&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4)),"")</f>
         <v/>
       </c>
-      <c r="E3" s="18" t="str">
+      <c r="E3" s="19" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A3-ボード!$B$4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="n">
+      <c r="A4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="n">
+      <c r="B4" s="19" t="n">
         <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A4/前提!$B$4</f>
         <v>16</v>
       </c>
-      <c r="C4" s="18" t="n">
+      <c r="C4" s="19" t="n">
         <f aca="false">IF(スマホ!B29="","",スマホ!B29)</f>
         <v>16</v>
       </c>
-      <c r="D4" s="18" t="str">
+      <c r="D4" s="19" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A4&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4)),"")</f>
         <v/>
       </c>
-      <c r="E4" s="18" t="str">
+      <c r="E4" s="19" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A4-ボード!$B$4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="n">
+      <c r="A5" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="19" t="n">
         <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A5/前提!$B$4</f>
         <v>14</v>
       </c>
-      <c r="C5" s="18" t="str">
+      <c r="C5" s="19" t="str">
         <f aca="false">IF(スマホ!B30="","",スマホ!B30)</f>
         <v/>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="19" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A5&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4)),"")</f>
         <v>14</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="19" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A5-ボード!$B$4)),"")</f>
         <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="n">
+      <c r="A6" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="19" t="n">
         <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A6/前提!$B$4</f>
         <v>12</v>
       </c>
-      <c r="C6" s="18" t="str">
+      <c r="C6" s="19" t="str">
         <f aca="false">IF(スマホ!B31="","",スマホ!B31)</f>
         <v/>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="19" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A6&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4)),"")</f>
         <v>12</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="19" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A6-ボード!$B$4)),"")</f>
         <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="n">
+      <c r="A7" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="19" t="n">
         <f aca="false">前提!$B$2+(前提!$B$3-前提!$B$2)*A7/前提!$B$4</f>
         <v>10</v>
       </c>
-      <c r="C7" s="18" t="str">
+      <c r="C7" s="19" t="str">
         <f aca="false">IF(スマホ!B32="","",スマホ!B32)</f>
         <v/>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="19" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A7&lt;=ボード!$B$4),"",ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4)),"")</f>
         <v>10</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4,ボード!$B$11=""),"",ボード!$B$5+ボード!$B$11*(A7-ボード!$B$4)),"")</f>
         <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3048,7 +3054,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3061,7 +3067,7 @@
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <f aca="false">IF(COUNT(記録!C2:C7)=0,"",INDEX(記録!A2:A7,MATCH(9.99E+307,記録!C2:C7)))</f>
         <v>3</v>
       </c>
@@ -3070,7 +3076,7 @@
       <c r="A5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="20" t="n">
         <f aca="false">IF(B4="","",INDEX(記録!C2:C7,MATCH(9.99E+307,記録!C2:C7)))</f>
         <v>16</v>
       </c>
@@ -3079,7 +3085,7 @@
       <c r="A6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="19" t="n">
         <f aca="false">前提!B3</f>
         <v>10</v>
       </c>
@@ -3088,7 +3094,7 @@
       <c r="A7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="21" t="n">
         <f aca="false">IF(OR(B4="",(前提!B3-前提!B2)=0),"",(B5-前提!B2)/(前提!B3-前提!B2))</f>
         <v>0.5</v>
       </c>
@@ -3097,7 +3103,7 @@
       <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="21" t="str">
+      <c r="B8" s="22" t="str">
         <f aca="false">IF(B4="","",IF((前提!B3-前提!B2)=0,"前提を確認（最初の値と目標が同じ）",IF((B5-INDEX(記録!B2:B7,B4))*SIGN((前提!B3-前提!B2))&gt;=0,"計画どおり、または先行","計画より遅れ")))</f>
         <v>計画どおり、または先行</v>
       </c>
@@ -3106,7 +3112,7 @@
       <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="18" t="n">
         <f aca="false">IF(B4="","",前提!B4-B4)</f>
         <v>3</v>
       </c>
@@ -3115,7 +3121,7 @@
       <c r="A10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="19" t="n">
+      <c r="B10" s="20" t="n">
         <f aca="false">IF(OR(B4="",(前提!B3-前提!B2)=0),"",IF((前提!B3-B5)*SIGN((前提!B3-前提!B2))&lt;=0,0,IF(B9&lt;=0,"",(前提!B3-B5)/B9)))</f>
         <v>-2</v>
       </c>
@@ -3124,7 +3130,7 @@
       <c r="A11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="19" t="n">
         <f aca="false">IF(COUNT(記録!C2:C7)&lt;2,"",(B5-前提!B2)/B4)</f>
         <v>-2</v>
       </c>
@@ -3133,7 +3139,7 @@
       <c r="A12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="21" t="str">
+      <c r="B12" s="22" t="str">
         <f aca="false">IF(B4="","",IF((前提!B3-前提!B2)=0,"前提を確認（最初の値と目標が同じ）",IF((前提!B3-B5)*SIGN((前提!B3-前提!B2))&lt;=0,"達成済み",IF(B9&lt;=0,"期限を過ぎています（前提の見直しが必要）",IF(COUNT(記録!C2:C7)&lt;2,"記録が2か月分以上で表示",IF(B11*SIGN((前提!B3-前提!B2))&lt;=0,"今のペースでは届かない（計画の見直しが必要）",IF(B4+(前提!B3-B5)/B11&lt;=前提!B4,"期限内（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）","期限より遅れる（"&amp;ROUNDUP(B4+(前提!B3-B5)/B11,0)&amp;"か月目ごろ）")))))))</f>
         <v>期限内（6か月目ごろ）</v>
       </c>
@@ -3142,7 +3148,7 @@
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="22" t="str">
+      <c r="B13" s="23" t="str">
         <f aca="false">IF(COUNTIF(記録!C2:C7,"&lt;0")&gt;0,"マイナスの値があります。確認してください",IF(B4="","実績を入力してください",IF(COUNT(記録!C2:C7)&lt;B4,"入力していない月があります（現在地は最後に入力した月で計算）","OK")))</f>
         <v>OK</v>
       </c>
@@ -3153,37 +3159,37 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="14" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="24" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B19" s="12" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="18" t="n">
         <f aca="false">スマホ!B34</f>
         <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="20" t="n">
+      <c r="B21" s="21" t="n">
         <f aca="false">IF(OR(B19="",B19&lt;=0),"",MIN(B20/B19,1))</f>
         <v>0.666666666666667</v>
       </c>
